--- a/보고서/인하대.xlsx
+++ b/보고서/인하대.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-14</t>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -59,10 +59,13 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>229 (pv)</t>
+    <t>290 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
+  </si>
+  <si>
+    <t>281 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">일일 평균 조회수 </t>
@@ -128,7 +131,7 @@
     <t>30대</t>
   </si>
   <si>
-    <t>29명</t>
+    <t>28명</t>
   </si>
   <si>
     <t>40대</t>
@@ -140,7 +143,7 @@
     <t>20대</t>
   </si>
   <si>
-    <t>4명</t>
+    <t>5명</t>
   </si>
   <si>
     <t>50대</t>
@@ -164,9 +167,6 @@
     <t>기타</t>
   </si>
   <si>
-    <t>5명</t>
-  </si>
-  <si>
     <t>블로그</t>
   </si>
   <si>
@@ -179,7 +179,7 @@
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.15~2026.06.14)</t>
+    <t>날짜(2026.03.22~2026.06.21)</t>
   </si>
   <si>
     <t>요일</t>
@@ -197,40 +197,61 @@
     <t>일</t>
   </si>
   <si>
-    <t>2026-06-13</t>
+    <t>2026-06-20</t>
   </si>
   <si>
     <t>토</t>
   </si>
   <si>
-    <t>2026-06-12</t>
+    <t>2026-06-19</t>
   </si>
   <si>
     <t>금</t>
   </si>
   <si>
-    <t>2026-06-11</t>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>목</t>
   </si>
   <si>
-    <t>2026-06-10</t>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>수</t>
   </si>
   <si>
-    <t>2026-06-09</t>
+    <t>2026-06-16</t>
   </si>
   <si>
     <t>화</t>
   </si>
   <si>
-    <t>2026-06-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>월</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
   </si>
   <si>
     <t>2026-06-07</t>
@@ -467,27 +488,6 @@
     <t>2026-03-22</t>
   </si>
   <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>콘텐츠 목록</t>
   </si>
   <si>
@@ -548,10 +548,10 @@
     <t>인하대역 재수</t>
   </si>
   <si>
-    <t>247공부환경</t>
+    <t>이투스247학원 인하대점</t>
   </si>
   <si>
-    <t>이투스247학원 인하대점</t>
+    <t>247공부환경</t>
   </si>
   <si>
     <t>247시스템</t>
@@ -1825,7 +1825,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
@@ -1835,10 +1835,10 @@
     <row r="16" spans="1:26" customHeight="1" ht="15">
       <c r="A16" s="3"/>
       <c r="B16" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
@@ -1857,7 +1857,7 @@
     <row r="18" spans="1:26" customHeight="1" ht="19.5">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
@@ -1868,15 +1868,15 @@
     <row r="19" spans="1:26" customHeight="1" ht="15">
       <c r="A19" s="24"/>
       <c r="B19" s="38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="38"/>
       <c r="F19" s="38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="24"/>
     </row>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
@@ -1900,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
@@ -1915,7 +1915,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
@@ -1929,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
@@ -2013,7 +2013,7 @@
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -2024,34 +2024,34 @@
     <row r="32" spans="1:26" customHeight="1" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="15">
       <c r="A33" s="52"/>
       <c r="B33" s="53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="55">
         <v>0.79166666666667</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" s="52"/>
     </row>
@@ -2059,30 +2059,30 @@
       <c r="A34" s="52"/>
       <c r="B34" s="56"/>
       <c r="C34" s="57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D34" s="58">
         <v>0.20833333333333</v>
       </c>
       <c r="E34" s="59"/>
       <c r="F34" s="57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="15">
       <c r="A35" s="52"/>
       <c r="B35" s="60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" s="61">
-        <v>0.60416666666667</v>
+        <v>0.58333333333333</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G35" s="52"/>
     </row>
@@ -2090,14 +2090,14 @@
       <c r="A36" s="52"/>
       <c r="B36" s="62"/>
       <c r="C36" s="44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D36" s="63">
         <v>0.27083333333333</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G36" s="52"/>
     </row>
@@ -2105,13 +2105,13 @@
       <c r="A37" s="52"/>
       <c r="B37" s="62"/>
       <c r="C37" s="54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D37" s="61">
-        <v>0.083333333333333</v>
+        <v>0.10416666666667</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G37" s="52"/>
     </row>
@@ -2119,30 +2119,30 @@
       <c r="A38" s="52"/>
       <c r="B38" s="64"/>
       <c r="C38" s="65" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D38" s="66">
         <v>0.041666666666667</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="65" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G38" s="52"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="15">
       <c r="A39" s="52"/>
       <c r="B39" s="67" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D39" s="61">
         <v>0.64285714285714</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="52"/>
     </row>
@@ -2150,14 +2150,14 @@
       <c r="A40" s="52"/>
       <c r="B40" s="62"/>
       <c r="C40" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D40" s="63">
         <v>0.23809523809524</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G40" s="52"/>
     </row>
@@ -2165,13 +2165,13 @@
       <c r="A41" s="52"/>
       <c r="B41" s="62"/>
       <c r="C41" s="54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D41" s="61">
         <v>0.11904761904762</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G41" s="52"/>
     </row>
@@ -3366,13 +3366,13 @@
         <v>58</v>
       </c>
       <c r="E3" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" s="82">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" s="82">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
@@ -3386,13 +3386,13 @@
         <v>60</v>
       </c>
       <c r="E4" s="86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="86">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z4" s="83"/>
     </row>
@@ -3406,13 +3406,13 @@
         <v>62</v>
       </c>
       <c r="E5" s="82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G5" s="82">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
@@ -3426,13 +3426,13 @@
         <v>64</v>
       </c>
       <c r="E6" s="86">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" s="86">
         <v>6</v>
       </c>
       <c r="G6" s="86">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
@@ -3446,13 +3446,13 @@
         <v>66</v>
       </c>
       <c r="E7" s="82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="82">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
@@ -3466,13 +3466,13 @@
         <v>68</v>
       </c>
       <c r="E8" s="86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="86">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G8" s="86">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z8" s="83"/>
     </row>
@@ -3486,13 +3486,13 @@
         <v>70</v>
       </c>
       <c r="E9" s="82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="82">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" s="82">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
@@ -3506,13 +3506,13 @@
         <v>58</v>
       </c>
       <c r="E10" s="86">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="86">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G10" s="86">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
@@ -3526,13 +3526,13 @@
         <v>60</v>
       </c>
       <c r="E11" s="82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="82">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
@@ -3546,13 +3546,13 @@
         <v>62</v>
       </c>
       <c r="E12" s="86">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" s="86">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G12" s="86">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
@@ -3566,13 +3566,13 @@
         <v>64</v>
       </c>
       <c r="E13" s="82">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F13" s="82">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G13" s="82">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
@@ -3586,13 +3586,13 @@
         <v>66</v>
       </c>
       <c r="E14" s="86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="86">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G14" s="86">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
@@ -3606,13 +3606,13 @@
         <v>68</v>
       </c>
       <c r="E15" s="82">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F15" s="82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G15" s="82">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
@@ -3626,13 +3626,13 @@
         <v>70</v>
       </c>
       <c r="E16" s="86">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" s="86">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G16" s="86">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
@@ -3646,13 +3646,13 @@
         <v>58</v>
       </c>
       <c r="E17" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="82">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
@@ -3666,13 +3666,13 @@
         <v>60</v>
       </c>
       <c r="E18" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" s="86">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
@@ -3686,13 +3686,13 @@
         <v>62</v>
       </c>
       <c r="E19" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F19" s="82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" s="82">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
@@ -3706,13 +3706,13 @@
         <v>64</v>
       </c>
       <c r="E20" s="86">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F20" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G20" s="86">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
@@ -3726,13 +3726,13 @@
         <v>66</v>
       </c>
       <c r="E21" s="82">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" s="82">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G21" s="82">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
@@ -3746,13 +3746,13 @@
         <v>68</v>
       </c>
       <c r="E22" s="86">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F22" s="86">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22" s="86">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="Z22" s="83"/>
     </row>
@@ -3766,13 +3766,13 @@
         <v>70</v>
       </c>
       <c r="E23" s="82">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" s="82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="82">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Z23" s="83"/>
     </row>
@@ -3786,13 +3786,13 @@
         <v>58</v>
       </c>
       <c r="E24" s="86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="83"/>
     </row>
@@ -3809,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="83"/>
     </row>
@@ -3826,13 +3826,13 @@
         <v>62</v>
       </c>
       <c r="E26" s="86">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" s="86">
         <v>2</v>
       </c>
       <c r="G26" s="86">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="83"/>
     </row>
@@ -3846,13 +3846,13 @@
         <v>64</v>
       </c>
       <c r="E27" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="82">
         <v>0</v>
       </c>
       <c r="G27" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="83"/>
     </row>
@@ -3866,13 +3866,13 @@
         <v>66</v>
       </c>
       <c r="E28" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z28" s="83"/>
     </row>
@@ -3886,13 +3886,13 @@
         <v>68</v>
       </c>
       <c r="E29" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z29" s="83"/>
     </row>
@@ -3906,13 +3906,13 @@
         <v>70</v>
       </c>
       <c r="E30" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="83"/>
     </row>
@@ -3926,13 +3926,13 @@
         <v>58</v>
       </c>
       <c r="E31" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="82">
         <v>0</v>
       </c>
       <c r="G31" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z31" s="83"/>
     </row>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="83"/>
     </row>
@@ -3966,13 +3966,13 @@
         <v>62</v>
       </c>
       <c r="E33" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F33" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z33" s="83"/>
     </row>
@@ -13514,7 +13514,7 @@
         <v>163</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E3" s="24">
         <v>6</v>
@@ -13548,7 +13548,7 @@
         <v>166</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E5" s="98">
         <v>2</v>
@@ -13582,7 +13582,7 @@
         <v>169</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E7" s="24">
         <v>14</v>
@@ -23574,7 +23574,7 @@
     </row>
     <row r="2" spans="1:26" customHeight="1" ht="18">
       <c r="A2" s="104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="105" t="s">
         <v>173</v>
@@ -23787,32 +23787,32 @@
         <v>0</v>
       </c>
       <c r="O5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" s="113">
         <f>SUM(B5:V5)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z5"/>
     </row>
@@ -23860,32 +23860,32 @@
         <v>0</v>
       </c>
       <c r="O6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="113">
         <f>SUM(B6:V6)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z6"/>
     </row>

--- a/보고서/인하대.xlsx
+++ b/보고서/인하대.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-21</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -35,7 +35,7 @@
     <t>캠페인 명</t>
   </si>
   <si>
-    <t>1/1차 - [인천] 이투스247학원 인하대점</t>
+    <t>1/1차 - [광주] 이투스247학원 광주수완점</t>
   </si>
   <si>
     <t>설명</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>290 (pv)</t>
+    <t>625 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
   </si>
   <si>
-    <t>281 (pv)</t>
+    <t>108 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">일일 평균 조회수 </t>
   </si>
   <si>
-    <t>9 (pv)</t>
+    <t>7 (pv)</t>
   </si>
   <si>
     <t>유입 키워드 TOP 10</t>
@@ -86,16 +86,34 @@
     <t>비율(%)</t>
   </si>
   <si>
-    <t>갤럭시북4울트라</t>
+    <t>광주광역시 이투스</t>
   </si>
   <si>
-    <t>이투스 인강 어때</t>
+    <t>광주독학재수학원</t>
   </si>
   <si>
-    <t>이투스 재수</t>
+    <t>광주재수학원</t>
   </si>
   <si>
-    <t>인하대 재수학원</t>
+    <t>수완동 스터디카페</t>
+  </si>
+  <si>
+    <t>이투스247수완점</t>
+  </si>
+  <si>
+    <t>수완지구 독재학원</t>
+  </si>
+  <si>
+    <t>이투스 광주수완</t>
+  </si>
+  <si>
+    <t>광주 광산구 관리형 독학학원</t>
+  </si>
+  <si>
+    <t>광주 이투스 독재</t>
+  </si>
+  <si>
+    <t>광주 이투스 수완 주차</t>
   </si>
   <si>
     <t>신청자 통계</t>
@@ -116,13 +134,13 @@
     <t>여자</t>
   </si>
   <si>
-    <t>38명</t>
+    <t>20명</t>
   </si>
   <si>
     <t>남자</t>
   </si>
   <si>
-    <t>10명</t>
+    <t>2명</t>
   </si>
   <si>
     <t>연령별</t>
@@ -131,40 +149,37 @@
     <t>30대</t>
   </si>
   <si>
-    <t>28명</t>
+    <t>15명</t>
   </si>
   <si>
     <t>40대</t>
   </si>
   <si>
-    <t>13명</t>
+    <t>4명</t>
   </si>
   <si>
     <t>20대</t>
   </si>
   <si>
-    <t>5명</t>
-  </si>
-  <si>
-    <t>50대</t>
-  </si>
-  <si>
-    <t>2명</t>
+    <t>3명</t>
   </si>
   <si>
     <t>지역별</t>
   </si>
   <si>
-    <t>인천</t>
+    <t>광주</t>
   </si>
   <si>
-    <t>27명</t>
-  </si>
-  <si>
-    <t>경기</t>
+    <t>13명</t>
   </si>
   <si>
     <t>기타</t>
+  </si>
+  <si>
+    <t>전북</t>
+  </si>
+  <si>
+    <t>1명</t>
   </si>
   <si>
     <t>블로그</t>
@@ -173,13 +188,13 @@
     <t>naver</t>
   </si>
   <si>
-    <t>48명</t>
+    <t>22명</t>
   </si>
   <si>
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.22~2026.06.21)</t>
+    <t>날짜(2026.05.19~2026.08.18)</t>
   </si>
   <si>
     <t>요일</t>
@@ -194,43 +209,217 @@
     <t>합산 조회수(PC+Mobile)</t>
   </si>
   <si>
+    <t>화</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>월</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
     <t>일</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>토</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>금</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>목</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>수</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t>2026-06-20</t>
   </si>
   <si>
-    <t>토</t>
-  </si>
-  <si>
     <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>금</t>
   </si>
   <si>
     <t>2026-06-18</t>
   </si>
   <si>
-    <t>목</t>
-  </si>
-  <si>
     <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>수</t>
   </si>
   <si>
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>화</t>
-  </si>
-  <si>
     <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>월</t>
   </si>
   <si>
     <t>2026-06-14</t>
@@ -314,180 +503,6 @@
     <t>2026-05-19</t>
   </si>
   <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
     <t>콘텐츠 목록</t>
   </si>
   <si>
@@ -506,31 +521,31 @@
     <t>댓글</t>
   </si>
   <si>
-    <t>이투스247학원 인하대점 미추홀구 독학재수학원으로 추천</t>
+    <t>광주 독학관리 반수학원 이투스247학원 광주수완점</t>
   </si>
   <si>
-    <t>릴리쥬스</t>
+    <t>judy13</t>
   </si>
   <si>
-    <t>https://blog.naver.com/silver_o0/224303642285</t>
+    <t>https://blog.naver.com/wings1324/224304113441</t>
   </si>
   <si>
-    <t>인하대 공부자극 독학재수학원 이투스247학원 인천인하대점 방문후기</t>
+    <t>수완지구 이투스247학원 광주 독학관리 잘 하는 곳</t>
   </si>
   <si>
-    <t>뚜미니뿌잉</t>
+    <t>yyiyuhyun</t>
   </si>
   <si>
-    <t>https://blog.naver.com/le4955/224302440503</t>
+    <t>https://blog.naver.com/yyiyuhyun/224303573025</t>
   </si>
   <si>
-    <t>이투스247학원 인하대점, 재수생루틴 잡기 좋은 인천 독학재수학원</t>
+    <t>이투스247학원 광주수완점 재수 반수 공부자극 확실한 독학관리</t>
   </si>
   <si>
-    <t>진이어스세상</t>
+    <t>하랑두랑</t>
   </si>
   <si>
-    <t>https://blog.naver.com/jin2usblog/224293711283</t>
+    <t>https://blog.naver.com/ever9472/224304969446</t>
   </si>
   <si>
     <t>총 합계</t>
@@ -545,28 +560,13 @@
     <t>총합</t>
   </si>
   <si>
-    <t>인하대역 재수</t>
+    <t>수완지구 반수</t>
   </si>
   <si>
-    <t>이투스247학원 인하대점</t>
+    <t>이투스247학원 광주수완점</t>
   </si>
   <si>
-    <t>247공부환경</t>
-  </si>
-  <si>
-    <t>247시스템</t>
-  </si>
-  <si>
-    <t>독학재수</t>
-  </si>
-  <si>
-    <t>독학재수학원</t>
-  </si>
-  <si>
-    <t>재수</t>
-  </si>
-  <si>
-    <t>재수학원추천</t>
+    <t>이투스247학원 후기</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
-        <v>0.25</v>
+        <v>0.30769230769231</v>
       </c>
       <c r="G20" s="24"/>
     </row>
@@ -1905,7 +1905,7 @@
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46">
-        <v>0.25</v>
+        <v>0.076923076923077</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
-        <v>0.25</v>
+        <v>0.076923076923077</v>
       </c>
       <c r="G22" s="24"/>
     </row>
@@ -1934,71 +1934,95 @@
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46">
-        <v>0.25</v>
+        <v>0.076923076923077</v>
       </c>
       <c r="G23" s="24"/>
     </row>
     <row r="24" spans="1:26" customHeight="1" ht="15">
       <c r="A24" s="24"/>
       <c r="B24" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="C24" s="15"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
+      <c r="F24" s="43">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G24" s="24"/>
     </row>
     <row r="25" spans="1:26" customHeight="1" ht="15">
       <c r="A25" s="24"/>
       <c r="B25" s="44">
-        <v>6.0</v>
-      </c>
-      <c r="C25" s="45"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>27</v>
+      </c>
       <c r="D25" s="27"/>
       <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
+      <c r="F25" s="46">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G25" s="24"/>
     </row>
     <row r="26" spans="1:26" customHeight="1" ht="15">
       <c r="A26" s="24"/>
       <c r="B26" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="C26" s="15"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
+      <c r="F26" s="43">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G26" s="24"/>
     </row>
     <row r="27" spans="1:26" customHeight="1" ht="15">
       <c r="A27" s="24"/>
       <c r="B27" s="44">
-        <v>8.0</v>
-      </c>
-      <c r="C27" s="45"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>29</v>
+      </c>
       <c r="D27" s="27"/>
       <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
+      <c r="F27" s="46">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G27" s="24"/>
     </row>
     <row r="28" spans="1:26" customHeight="1" ht="15">
       <c r="A28" s="24"/>
       <c r="B28" s="41">
-        <v>9.0</v>
-      </c>
-      <c r="C28" s="15"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="43">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:26" customHeight="1" ht="15">
       <c r="A29" s="24"/>
       <c r="B29" s="47">
-        <v>10.0</v>
-      </c>
-      <c r="C29" s="48"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>31</v>
+      </c>
       <c r="D29" s="37"/>
       <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
+      <c r="F29" s="49">
+        <v>0.076923076923077</v>
+      </c>
       <c r="G29" s="24"/>
     </row>
     <row r="30" spans="1:26" customHeight="1" ht="13.5">
@@ -2013,7 +2037,7 @@
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -2024,34 +2048,34 @@
     <row r="32" spans="1:26" customHeight="1" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="50" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D32" s="51" t="s">
         <v>21</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="50" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="15">
       <c r="A33" s="52"/>
       <c r="B33" s="53" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D33" s="55">
-        <v>0.79166666666667</v>
+        <v>0.90909090909091</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="54" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G33" s="52"/>
     </row>
@@ -2059,30 +2083,30 @@
       <c r="A34" s="52"/>
       <c r="B34" s="56"/>
       <c r="C34" s="57" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D34" s="58">
-        <v>0.20833333333333</v>
+        <v>0.090909090909091</v>
       </c>
       <c r="E34" s="59"/>
       <c r="F34" s="57" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="15">
       <c r="A35" s="52"/>
       <c r="B35" s="60" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D35" s="61">
-        <v>0.58333333333333</v>
+        <v>0.68181818181818</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G35" s="52"/>
     </row>
@@ -2090,14 +2114,14 @@
       <c r="A36" s="52"/>
       <c r="B36" s="62"/>
       <c r="C36" s="44" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D36" s="63">
-        <v>0.27083333333333</v>
+        <v>0.18181818181818</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="44" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G36" s="52"/>
     </row>
@@ -2105,44 +2129,38 @@
       <c r="A37" s="52"/>
       <c r="B37" s="62"/>
       <c r="C37" s="54" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D37" s="61">
-        <v>0.10416666666667</v>
+        <v>0.13636363636364</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G37" s="52"/>
     </row>
     <row r="38" spans="1:26" customHeight="1" ht="15">
       <c r="A38" s="52"/>
       <c r="B38" s="64"/>
-      <c r="C38" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="66">
-        <v>0.041666666666667</v>
-      </c>
+      <c r="C38" s="65"/>
+      <c r="D38" s="66"/>
       <c r="E38" s="34"/>
-      <c r="F38" s="65" t="s">
-        <v>43</v>
-      </c>
+      <c r="F38" s="65"/>
       <c r="G38" s="52"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="15">
       <c r="A39" s="52"/>
       <c r="B39" s="67" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D39" s="61">
-        <v>0.64285714285714</v>
+        <v>0.8125</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G39" s="52"/>
     </row>
@@ -2150,14 +2168,14 @@
       <c r="A40" s="52"/>
       <c r="B40" s="62"/>
       <c r="C40" s="44" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D40" s="63">
-        <v>0.23809523809524</v>
+        <v>0.125</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="44" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G40" s="52"/>
     </row>
@@ -2165,13 +2183,13 @@
       <c r="A41" s="52"/>
       <c r="B41" s="62"/>
       <c r="C41" s="54" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D41" s="61">
-        <v>0.11904761904762</v>
+        <v>0.0625</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G41" s="52"/>
     </row>
@@ -2187,17 +2205,17 @@
     <row r="43" spans="1:26" customHeight="1" ht="15">
       <c r="A43" s="52"/>
       <c r="B43" s="68" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D43" s="55">
         <v>1</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="54" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="69"/>
@@ -3328,7 +3346,7 @@
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="74"/>
       <c r="B1" s="75" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -3339,20 +3357,20 @@
     <row r="2" spans="1:26" customHeight="1" ht="30">
       <c r="A2" s="76"/>
       <c r="B2" s="39" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="77" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E2" s="77" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F2" s="78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H2" s="69"/>
     </row>
@@ -3363,27 +3381,27 @@
       </c>
       <c r="C3"/>
       <c r="D3" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E3" s="82">
         <v>0</v>
       </c>
       <c r="F3" s="82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3" s="82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
     <row r="4" spans="1:26" customHeight="1" ht="19.5">
       <c r="A4" s="79"/>
       <c r="B4" s="84" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E4" s="86">
         <v>0</v>
@@ -3399,457 +3417,457 @@
     <row r="5" spans="1:26" customHeight="1" ht="19.5">
       <c r="A5" s="79"/>
       <c r="B5" s="80" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C5"/>
       <c r="D5" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E5" s="82">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5" s="82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="82">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
     <row r="6" spans="1:26" customHeight="1" ht="19.5">
       <c r="A6" s="79"/>
       <c r="B6" s="84" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E6" s="86">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6" s="86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6" s="86">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
     <row r="7" spans="1:26" customHeight="1" ht="19.5">
       <c r="A7" s="79"/>
       <c r="B7" s="80" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E7" s="82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7" s="82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
     <row r="8" spans="1:26" customHeight="1" ht="19.5">
       <c r="A8" s="79"/>
       <c r="B8" s="84" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E8" s="86">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="86">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="83"/>
     </row>
     <row r="9" spans="1:26" customHeight="1" ht="19.5">
       <c r="A9" s="79"/>
       <c r="B9" s="80" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C9"/>
       <c r="D9" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E9" s="82">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
     <row r="10" spans="1:26" customHeight="1" ht="19.5">
       <c r="A10" s="79"/>
       <c r="B10" s="84" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E10" s="86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F10" s="86">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G10" s="86">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
     <row r="11" spans="1:26" customHeight="1" ht="19.5">
       <c r="A11" s="79"/>
       <c r="B11" s="80" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11"/>
       <c r="D11" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E11" s="82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="82">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="82">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
     <row r="12" spans="1:26" customHeight="1" ht="19.5">
       <c r="A12" s="79"/>
       <c r="B12" s="84" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" s="86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F12" s="86">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G12" s="86">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
     <row r="13" spans="1:26" customHeight="1" ht="19.5">
       <c r="A13" s="79"/>
       <c r="B13" s="80" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C13"/>
       <c r="D13" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E13" s="82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="82">
+        <v>3</v>
+      </c>
+      <c r="G13" s="82">
         <v>6</v>
-      </c>
-      <c r="G13" s="82">
-        <v>11</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
     <row r="14" spans="1:26" customHeight="1" ht="19.5">
       <c r="A14" s="79"/>
       <c r="B14" s="84" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E14" s="86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" s="86">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G14" s="86">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
     <row r="15" spans="1:26" customHeight="1" ht="19.5">
       <c r="A15" s="79"/>
       <c r="B15" s="80" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15"/>
       <c r="D15" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E15" s="82">
+        <v>0</v>
+      </c>
+      <c r="F15" s="82">
         <v>5</v>
       </c>
-      <c r="F15" s="82">
-        <v>7</v>
-      </c>
       <c r="G15" s="82">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
     <row r="16" spans="1:26" customHeight="1" ht="19.5">
       <c r="A16" s="79"/>
       <c r="B16" s="84" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E16" s="86">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F16" s="86">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16" s="86">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
     <row r="17" spans="1:26" customHeight="1" ht="19.5">
       <c r="A17" s="79"/>
       <c r="B17" s="80" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17"/>
       <c r="D17" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E17" s="82">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" s="82">
+        <v>1</v>
+      </c>
+      <c r="G17" s="82">
         <v>2</v>
-      </c>
-      <c r="G17" s="82">
-        <v>9</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
     <row r="18" spans="1:26" customHeight="1" ht="19.5">
       <c r="A18" s="79"/>
       <c r="B18" s="84" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E18" s="86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="86">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G18" s="86">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
     <row r="19" spans="1:26" customHeight="1" ht="19.5">
       <c r="A19" s="79"/>
       <c r="B19" s="80" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C19"/>
       <c r="D19" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" s="82">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F19" s="82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="82">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
     <row r="20" spans="1:26" customHeight="1" ht="19.5">
       <c r="A20" s="79"/>
       <c r="B20" s="84" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E20" s="86">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F20" s="86">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G20" s="86">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
     <row r="21" spans="1:26" customHeight="1" ht="19.5">
       <c r="A21" s="79"/>
       <c r="B21" s="80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C21"/>
       <c r="D21" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E21" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F21" s="82">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G21" s="82">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
     <row r="22" spans="1:26" customHeight="1" ht="19.5">
       <c r="A22" s="79"/>
       <c r="B22" s="84" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E22" s="86">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F22" s="86">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G22" s="86">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="83"/>
     </row>
     <row r="23" spans="1:26" customHeight="1" ht="19.5">
       <c r="A23" s="79"/>
       <c r="B23" s="80" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C23"/>
       <c r="D23" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E23" s="82">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F23" s="82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="82">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z23" s="83"/>
     </row>
     <row r="24" spans="1:26" customHeight="1" ht="19.5">
       <c r="A24" s="79"/>
       <c r="B24" s="84" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E24" s="86">
         <v>0</v>
       </c>
       <c r="F24" s="86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z24" s="83"/>
     </row>
     <row r="25" spans="1:26" customHeight="1" ht="19.5">
       <c r="A25" s="79"/>
       <c r="B25" s="80" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E25" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z25" s="83"/>
     </row>
     <row r="26" spans="1:26" customHeight="1" ht="19.5">
       <c r="A26" s="79"/>
       <c r="B26" s="84" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E26" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="86">
         <v>2</v>
       </c>
       <c r="G26" s="86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z26" s="83"/>
     </row>
     <row r="27" spans="1:26" customHeight="1" ht="19.5">
       <c r="A27" s="79"/>
       <c r="B27" s="80" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E27" s="82">
+        <v>0</v>
+      </c>
+      <c r="F27" s="82">
         <v>2</v>
-      </c>
-      <c r="F27" s="82">
-        <v>0</v>
       </c>
       <c r="G27" s="82">
         <v>2</v>
@@ -3859,1071 +3877,1071 @@
     <row r="28" spans="1:26" customHeight="1" ht="19.5">
       <c r="A28" s="79"/>
       <c r="B28" s="84" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E28" s="86">
+        <v>0</v>
+      </c>
+      <c r="F28" s="86">
         <v>2</v>
       </c>
-      <c r="F28" s="86">
-        <v>1</v>
-      </c>
       <c r="G28" s="86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z28" s="83"/>
     </row>
     <row r="29" spans="1:26" customHeight="1" ht="19.5">
       <c r="A29" s="79"/>
       <c r="B29" s="80" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E29" s="82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="82">
         <v>1</v>
       </c>
       <c r="G29" s="82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="83"/>
     </row>
     <row r="30" spans="1:26" customHeight="1" ht="19.5">
       <c r="A30" s="79"/>
       <c r="B30" s="84" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E30" s="86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="86">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" s="86">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z30" s="83"/>
     </row>
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="79"/>
       <c r="B31" s="80" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E31" s="82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="83"/>
     </row>
     <row r="32" spans="1:26" customHeight="1" ht="19.5">
       <c r="A32" s="79"/>
       <c r="B32" s="84" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E32" s="86">
         <v>0</v>
       </c>
       <c r="F32" s="86">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G32" s="86">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z32" s="83"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="19.5">
       <c r="A33" s="79"/>
       <c r="B33" s="80" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C33"/>
       <c r="D33" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E33" s="82">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F33" s="82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="82">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z33" s="83"/>
     </row>
     <row r="34" spans="1:26" customHeight="1" ht="19.5">
       <c r="A34" s="79"/>
       <c r="B34" s="84" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E34" s="86">
         <v>0</v>
       </c>
       <c r="F34" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="83"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="19.5">
       <c r="A35" s="79"/>
       <c r="B35" s="80" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E35" s="82">
         <v>0</v>
       </c>
       <c r="F35" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="83"/>
     </row>
     <row r="36" spans="1:26" customHeight="1" ht="19.5">
       <c r="A36" s="79"/>
       <c r="B36" s="84" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E36" s="86">
         <v>0</v>
       </c>
       <c r="F36" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z36" s="83"/>
     </row>
     <row r="37" spans="1:26" customHeight="1" ht="19.5">
       <c r="A37" s="79"/>
       <c r="B37" s="80" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C37"/>
       <c r="D37" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E37" s="82">
         <v>0</v>
       </c>
       <c r="F37" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="83"/>
     </row>
     <row r="38" spans="1:26" customHeight="1" ht="19.5">
       <c r="A38" s="79"/>
       <c r="B38" s="84" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E38" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F38" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G38" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z38" s="83"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="19.5">
       <c r="A39" s="79"/>
       <c r="B39" s="80" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E39" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z39" s="83"/>
     </row>
     <row r="40" spans="1:26" customHeight="1" ht="19.5">
       <c r="A40" s="79"/>
       <c r="B40" s="84" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E40" s="86">
         <v>0</v>
       </c>
       <c r="F40" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G40" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z40" s="83"/>
     </row>
     <row r="41" spans="1:26" customHeight="1" ht="19.5">
       <c r="A41" s="79"/>
       <c r="B41" s="80" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C41"/>
       <c r="D41" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E41" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G41" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z41" s="83"/>
     </row>
     <row r="42" spans="1:26" customHeight="1" ht="19.5">
       <c r="A42" s="79"/>
       <c r="B42" s="84" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E42" s="86">
         <v>0</v>
       </c>
       <c r="F42" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G42" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z42" s="83"/>
     </row>
     <row r="43" spans="1:26" customHeight="1" ht="19.5">
       <c r="A43" s="79"/>
       <c r="B43" s="80" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C43"/>
       <c r="D43" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E43" s="82">
         <v>0</v>
       </c>
       <c r="F43" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="83"/>
     </row>
     <row r="44" spans="1:26" customHeight="1" ht="19.5">
       <c r="A44" s="79"/>
       <c r="B44" s="84" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C44" s="26"/>
       <c r="D44" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E44" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z44" s="83"/>
     </row>
     <row r="45" spans="1:26" customHeight="1" ht="19.5">
       <c r="A45" s="79"/>
       <c r="B45" s="80" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C45"/>
       <c r="D45" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E45" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z45" s="83"/>
     </row>
     <row r="46" spans="1:26" customHeight="1" ht="19.5">
       <c r="A46" s="79"/>
       <c r="B46" s="84" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E46" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G46" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z46" s="83"/>
     </row>
     <row r="47" spans="1:26" customHeight="1" ht="19.5">
       <c r="A47" s="79"/>
       <c r="B47" s="80" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C47"/>
       <c r="D47" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E47" s="82">
         <v>0</v>
       </c>
       <c r="F47" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z47" s="83"/>
     </row>
     <row r="48" spans="1:26" customHeight="1" ht="19.5">
       <c r="A48" s="79"/>
       <c r="B48" s="84" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E48" s="86">
         <v>0</v>
       </c>
       <c r="F48" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z48" s="83"/>
     </row>
     <row r="49" spans="1:26" customHeight="1" ht="19.5">
       <c r="A49" s="79"/>
       <c r="B49" s="80" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C49"/>
       <c r="D49" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E49" s="82">
         <v>0</v>
       </c>
       <c r="F49" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G49" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z49" s="83"/>
     </row>
     <row r="50" spans="1:26" customHeight="1" ht="19.5">
       <c r="A50" s="79"/>
       <c r="B50" s="84" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C50" s="26"/>
       <c r="D50" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E50" s="86">
         <v>0</v>
       </c>
       <c r="F50" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G50" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z50" s="83"/>
     </row>
     <row r="51" spans="1:26" customHeight="1" ht="19.5">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E51" s="82">
         <v>0</v>
       </c>
       <c r="F51" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G51" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z51" s="83"/>
     </row>
     <row r="52" spans="1:26" customHeight="1" ht="19.5">
       <c r="A52" s="79"/>
       <c r="B52" s="84" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C52" s="26"/>
       <c r="D52" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E52" s="86">
         <v>0</v>
       </c>
       <c r="F52" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G52" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z52" s="83"/>
     </row>
     <row r="53" spans="1:26" customHeight="1" ht="19.5">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C53"/>
       <c r="D53" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E53" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="82">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G53" s="82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z53" s="83"/>
     </row>
     <row r="54" spans="1:26" customHeight="1" ht="19.5">
       <c r="A54" s="79"/>
       <c r="B54" s="84" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E54" s="86">
         <v>0</v>
       </c>
       <c r="F54" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G54" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z54" s="83"/>
     </row>
     <row r="55" spans="1:26" customHeight="1" ht="19.5">
       <c r="A55" s="79"/>
       <c r="B55" s="80" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C55"/>
       <c r="D55" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E55" s="82">
         <v>0</v>
       </c>
       <c r="F55" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G55" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z55" s="83"/>
     </row>
     <row r="56" spans="1:26" customHeight="1" ht="19.5">
       <c r="A56" s="79"/>
       <c r="B56" s="84" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E56" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G56" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z56" s="83"/>
     </row>
     <row r="57" spans="1:26" customHeight="1" ht="19.5">
       <c r="A57" s="79"/>
       <c r="B57" s="80" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C57"/>
       <c r="D57" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E57" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F57" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z57" s="83"/>
     </row>
     <row r="58" spans="1:26" customHeight="1" ht="19.5">
       <c r="A58" s="79"/>
       <c r="B58" s="84" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E58" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F58" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G58" s="86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z58" s="83"/>
     </row>
     <row r="59" spans="1:26" customHeight="1" ht="19.5">
       <c r="A59" s="79"/>
       <c r="B59" s="80" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C59"/>
       <c r="D59" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E59" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F59" s="82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G59" s="82">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z59" s="83"/>
     </row>
     <row r="60" spans="1:26" customHeight="1" ht="19.5">
       <c r="A60" s="79"/>
       <c r="B60" s="84" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C60" s="26"/>
       <c r="D60" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E60" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F60" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G60" s="86">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z60" s="83"/>
     </row>
     <row r="61" spans="1:26" customHeight="1" ht="19.5">
       <c r="A61" s="79"/>
       <c r="B61" s="80" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C61"/>
       <c r="D61" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E61" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F61" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G61" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z61" s="83"/>
     </row>
     <row r="62" spans="1:26" customHeight="1" ht="19.5">
       <c r="A62" s="79"/>
       <c r="B62" s="84" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C62" s="26"/>
       <c r="D62" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E62" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z62" s="83"/>
     </row>
     <row r="63" spans="1:26" customHeight="1" ht="19.5">
       <c r="A63" s="79"/>
       <c r="B63" s="80" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C63"/>
       <c r="D63" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E63" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F63" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G63" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z63" s="83"/>
     </row>
     <row r="64" spans="1:26" customHeight="1" ht="19.5">
       <c r="A64" s="79"/>
       <c r="B64" s="84" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C64" s="26"/>
       <c r="D64" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E64" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G64" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z64" s="83"/>
     </row>
     <row r="65" spans="1:26" customHeight="1" ht="19.5">
       <c r="A65" s="79"/>
       <c r="B65" s="80" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C65"/>
       <c r="D65" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E65" s="82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F65" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G65" s="82">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z65" s="83"/>
     </row>
     <row r="66" spans="1:26" customHeight="1" ht="19.5">
       <c r="A66" s="79"/>
       <c r="B66" s="84" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C66" s="26"/>
       <c r="D66" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E66" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F66" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G66" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z66" s="83"/>
     </row>
     <row r="67" spans="1:26" customHeight="1" ht="19.5">
       <c r="A67" s="79"/>
       <c r="B67" s="80" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C67"/>
       <c r="D67" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E67" s="82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F67" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G67" s="82">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z67" s="83"/>
     </row>
     <row r="68" spans="1:26" customHeight="1" ht="19.5">
       <c r="A68" s="79"/>
       <c r="B68" s="84" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C68" s="26"/>
       <c r="D68" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E68" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F68" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G68" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z68" s="83"/>
     </row>
     <row r="69" spans="1:26" customHeight="1" ht="19.5">
       <c r="A69" s="79"/>
       <c r="B69" s="80" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C69"/>
       <c r="D69" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E69" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G69" s="82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z69" s="83"/>
     </row>
     <row r="70" spans="1:26" customHeight="1" ht="19.5">
       <c r="A70" s="79"/>
       <c r="B70" s="84" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C70" s="26"/>
       <c r="D70" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E70" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F70" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G70" s="86">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z70" s="83"/>
     </row>
     <row r="71" spans="1:26" customHeight="1" ht="19.5">
       <c r="A71" s="79"/>
       <c r="B71" s="80" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C71"/>
       <c r="D71" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E71" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G71" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z71" s="83"/>
     </row>
     <row r="72" spans="1:26" customHeight="1" ht="19.5">
       <c r="A72" s="79"/>
       <c r="B72" s="84" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C72" s="26"/>
       <c r="D72" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E72" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F72" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G72" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z72" s="83"/>
     </row>
     <row r="73" spans="1:26" customHeight="1" ht="19.5">
       <c r="A73" s="79"/>
       <c r="B73" s="80" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C73"/>
       <c r="D73" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E73" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F73" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z73" s="83"/>
     </row>
     <row r="74" spans="1:26" customHeight="1" ht="19.5">
       <c r="A74" s="79"/>
       <c r="B74" s="84" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C74" s="26"/>
       <c r="D74" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E74" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G74" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z74" s="83"/>
     </row>
     <row r="75" spans="1:26" customHeight="1" ht="19.5">
       <c r="A75" s="79"/>
       <c r="B75" s="80" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C75"/>
       <c r="D75" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E75" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F75" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G75" s="82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z75" s="83"/>
     </row>
     <row r="76" spans="1:26" customHeight="1" ht="19.5">
       <c r="A76" s="79"/>
       <c r="B76" s="84" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C76" s="26"/>
       <c r="D76" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E76" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F76" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z76" s="83"/>
     </row>
     <row r="77" spans="1:26" customHeight="1" ht="19.5">
       <c r="A77" s="79"/>
       <c r="B77" s="80" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C77"/>
       <c r="D77" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E77" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F77" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G77" s="82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z77" s="83"/>
     </row>
     <row r="78" spans="1:26" customHeight="1" ht="19.5">
       <c r="A78" s="79"/>
       <c r="B78" s="84" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C78" s="26"/>
       <c r="D78" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E78" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F78" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G78" s="86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z78" s="83"/>
     </row>
     <row r="79" spans="1:26" customHeight="1" ht="19.5">
       <c r="A79" s="79"/>
       <c r="B79" s="80" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C79"/>
       <c r="D79" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E79" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F79" s="82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G79" s="82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z79" s="83"/>
     </row>
     <row r="80" spans="1:26" customHeight="1" ht="19.5">
       <c r="A80" s="79"/>
       <c r="B80" s="84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C80" s="26"/>
       <c r="D80" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E80" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F80" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G80" s="86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z80" s="83"/>
     </row>
     <row r="81" spans="1:26" customHeight="1" ht="19.5">
       <c r="A81" s="79"/>
       <c r="B81" s="80" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C81"/>
       <c r="D81" s="81" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E81" s="82">
         <v>0</v>
@@ -4939,11 +4957,11 @@
     <row r="82" spans="1:26" customHeight="1" ht="19.5">
       <c r="A82" s="79"/>
       <c r="B82" s="84" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C82" s="26"/>
       <c r="D82" s="85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E82" s="86">
         <v>0</v>
@@ -4959,11 +4977,11 @@
     <row r="83" spans="1:26" customHeight="1" ht="19.5">
       <c r="A83" s="79"/>
       <c r="B83" s="80" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C83"/>
       <c r="D83" s="81" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E83" s="82">
         <v>0</v>
@@ -4979,11 +4997,11 @@
     <row r="84" spans="1:26" customHeight="1" ht="19.5">
       <c r="A84" s="79"/>
       <c r="B84" s="84" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C84" s="26"/>
       <c r="D84" s="85" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E84" s="86">
         <v>0</v>
@@ -4999,11 +5017,11 @@
     <row r="85" spans="1:26" customHeight="1" ht="19.5">
       <c r="A85" s="79"/>
       <c r="B85" s="80" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C85"/>
       <c r="D85" s="81" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E85" s="82">
         <v>0</v>
@@ -5019,11 +5037,11 @@
     <row r="86" spans="1:26" customHeight="1" ht="19.5">
       <c r="A86" s="79"/>
       <c r="B86" s="84" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C86" s="26"/>
       <c r="D86" s="85" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E86" s="86">
         <v>0</v>
@@ -5039,11 +5057,11 @@
     <row r="87" spans="1:26" customHeight="1" ht="19.5">
       <c r="A87" s="79"/>
       <c r="B87" s="80" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C87"/>
       <c r="D87" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E87" s="82">
         <v>0</v>
@@ -5059,11 +5077,11 @@
     <row r="88" spans="1:26" customHeight="1" ht="19.5">
       <c r="A88" s="79"/>
       <c r="B88" s="84" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C88" s="26"/>
       <c r="D88" s="85" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E88" s="86">
         <v>0</v>
@@ -5079,11 +5097,11 @@
     <row r="89" spans="1:26" customHeight="1" ht="19.5">
       <c r="A89" s="79"/>
       <c r="B89" s="80" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C89"/>
       <c r="D89" s="81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E89" s="82">
         <v>0</v>
@@ -5099,11 +5117,11 @@
     <row r="90" spans="1:26" customHeight="1" ht="19.5">
       <c r="A90" s="79"/>
       <c r="B90" s="84" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C90" s="26"/>
       <c r="D90" s="85" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E90" s="86">
         <v>0</v>
@@ -5119,11 +5137,11 @@
     <row r="91" spans="1:26" customHeight="1" ht="19.5">
       <c r="A91" s="79"/>
       <c r="B91" s="80" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C91"/>
       <c r="D91" s="81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E91" s="82">
         <v>0</v>
@@ -5139,11 +5157,11 @@
     <row r="92" spans="1:26" customHeight="1" ht="19.5">
       <c r="A92" s="79"/>
       <c r="B92" s="84" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C92" s="26"/>
       <c r="D92" s="85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E92" s="86">
         <v>0</v>
@@ -5159,11 +5177,11 @@
     <row r="93" spans="1:26" customHeight="1" ht="19.5">
       <c r="A93" s="79"/>
       <c r="B93" s="80" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C93"/>
       <c r="D93" s="81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E93" s="82">
         <v>0</v>
@@ -5179,11 +5197,11 @@
     <row r="94" spans="1:26" customHeight="1" ht="19.5">
       <c r="A94" s="79"/>
       <c r="B94" s="84" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C94" s="26"/>
       <c r="D94" s="85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E94" s="86">
         <v>0</v>
@@ -13476,7 +13494,7 @@
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="89"/>
       <c r="B1" s="90" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
@@ -13488,19 +13506,19 @@
     <row r="2" spans="1:26" customHeight="1" ht="24.75">
       <c r="A2" s="83"/>
       <c r="B2" s="91" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D2" s="91" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F2" s="91" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G2" s="83"/>
       <c r="H2" s="89"/>
@@ -13508,13 +13526,13 @@
     <row r="3" spans="1:26" customHeight="1" ht="27.75">
       <c r="A3" s="89"/>
       <c r="B3" s="93" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="E3" s="24">
         <v>6</v>
@@ -13529,7 +13547,7 @@
     <row r="4" spans="1:26" customHeight="1" ht="15">
       <c r="A4" s="89"/>
       <c r="B4" s="96" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -13542,16 +13560,16 @@
     <row r="5" spans="1:26" customHeight="1" ht="27.75">
       <c r="A5" s="89"/>
       <c r="B5" s="97" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E5" s="98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="98">
         <v>1</v>
@@ -13563,7 +13581,7 @@
     <row r="6" spans="1:26" customHeight="1" ht="15">
       <c r="A6" s="95"/>
       <c r="B6" s="100" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -13576,19 +13594,19 @@
     <row r="7" spans="1:26" customHeight="1" ht="27.75">
       <c r="A7" s="89"/>
       <c r="B7" s="93" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="E7" s="24">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F7" s="24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="95"/>
       <c r="H7" s="89"/>
@@ -13597,7 +13615,7 @@
     <row r="8" spans="1:26" customHeight="1" ht="15">
       <c r="A8" s="89"/>
       <c r="B8" s="96" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -13610,17 +13628,17 @@
     <row r="9" spans="1:26" customHeight="1" ht="24">
       <c r="A9" s="89"/>
       <c r="B9" s="101" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="27"/>
       <c r="E9" s="102">
         <f>SUM(E3:E8)</f>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F9" s="102">
         <f>SUM(F3:F8)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="89"/>
       <c r="H9" s="89"/>
@@ -23539,7 +23557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="14.43" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.86" customWidth="true" style="0"/>
@@ -23569,7 +23587,7 @@
   <sheetData>
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="103" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:26" customHeight="1" ht="18">
@@ -23577,7 +23595,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C2" s="106"/>
       <c r="D2" s="106"/>
@@ -23600,7 +23618,7 @@
       <c r="U2" s="106"/>
       <c r="V2" s="107"/>
       <c r="W2" s="108" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:26" customHeight="1" ht="24.75">
@@ -23672,7 +23690,7 @@
     </row>
     <row r="4" spans="1:26" customHeight="1" ht="18">
       <c r="A4" s="112" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B4" s="113">
         <v>0</v>
@@ -23696,34 +23714,34 @@
         <v>0</v>
       </c>
       <c r="I4" s="113">
+        <v>0</v>
+      </c>
+      <c r="J4" s="113">
+        <v>0</v>
+      </c>
+      <c r="K4" s="113">
+        <v>0</v>
+      </c>
+      <c r="L4" s="113">
+        <v>0</v>
+      </c>
+      <c r="M4" s="113">
+        <v>0</v>
+      </c>
+      <c r="N4" s="113">
+        <v>0</v>
+      </c>
+      <c r="O4" s="113">
+        <v>0</v>
+      </c>
+      <c r="P4" s="113">
         <v>1</v>
-      </c>
-      <c r="J4" s="113">
-        <v>1</v>
-      </c>
-      <c r="K4" s="113">
-        <v>1</v>
-      </c>
-      <c r="L4" s="113">
-        <v>1</v>
-      </c>
-      <c r="M4" s="113">
-        <v>2</v>
-      </c>
-      <c r="N4" s="113">
-        <v>1</v>
-      </c>
-      <c r="O4" s="113">
-        <v>2</v>
-      </c>
-      <c r="P4" s="113">
-        <v>2</v>
       </c>
       <c r="Q4" s="113">
         <v>2</v>
       </c>
       <c r="R4" s="113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" s="113">
         <v>2</v>
@@ -23739,13 +23757,13 @@
       </c>
       <c r="W4" s="113">
         <f>SUM(B4:V4)</f>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Z4"/>
     </row>
     <row r="5" spans="1:26" customHeight="1" ht="18">
       <c r="A5" s="114" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B5" s="115">
         <v>0</v>
@@ -23790,35 +23808,35 @@
         <v>0</v>
       </c>
       <c r="P5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="113">
         <f>SUM(B5:V5)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z5"/>
     </row>
     <row r="6" spans="1:26" customHeight="1" ht="18">
       <c r="A6" s="112" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B6" s="113">
         <v>0</v>
@@ -23860,399 +23878,159 @@
         <v>0</v>
       </c>
       <c r="O6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="113">
         <f>SUM(B6:V6)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z6"/>
     </row>
-    <row r="7" spans="1:26" customHeight="1" ht="18">
-      <c r="A7" s="114" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="115">
-        <v>0</v>
-      </c>
-      <c r="C7" s="115">
-        <v>0</v>
-      </c>
-      <c r="D7" s="115">
-        <v>0</v>
-      </c>
-      <c r="E7" s="115">
-        <v>0</v>
-      </c>
-      <c r="F7" s="115">
-        <v>0</v>
-      </c>
-      <c r="G7" s="115">
-        <v>0</v>
-      </c>
-      <c r="H7" s="115">
-        <v>0</v>
-      </c>
-      <c r="I7" s="115">
-        <v>0</v>
-      </c>
-      <c r="J7" s="115">
-        <v>0</v>
-      </c>
-      <c r="K7" s="115">
-        <v>0</v>
-      </c>
-      <c r="L7" s="115">
-        <v>0</v>
-      </c>
-      <c r="M7" s="115">
-        <v>0</v>
-      </c>
-      <c r="N7" s="115">
-        <v>0</v>
-      </c>
-      <c r="O7" s="115">
-        <v>0</v>
-      </c>
-      <c r="P7" s="115">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="115">
-        <v>0</v>
-      </c>
-      <c r="R7" s="115">
-        <v>0</v>
-      </c>
-      <c r="S7" s="115">
-        <v>0</v>
-      </c>
-      <c r="T7" s="115">
-        <v>0</v>
-      </c>
-      <c r="U7" s="115">
-        <v>0</v>
-      </c>
-      <c r="V7" s="115">
-        <v>0</v>
-      </c>
-      <c r="W7" s="113">
-        <f>SUM(B7:V7)</f>
-        <v>0</v>
-      </c>
-      <c r="Z7"/>
-    </row>
-    <row r="8" spans="1:26" customHeight="1" ht="18">
-      <c r="A8" s="112" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="113">
-        <v>0</v>
-      </c>
-      <c r="C8" s="113">
-        <v>0</v>
-      </c>
-      <c r="D8" s="113">
-        <v>0</v>
-      </c>
-      <c r="E8" s="113">
-        <v>0</v>
-      </c>
-      <c r="F8" s="113">
-        <v>0</v>
-      </c>
-      <c r="G8" s="113">
-        <v>0</v>
-      </c>
-      <c r="H8" s="113">
-        <v>0</v>
-      </c>
-      <c r="I8" s="113">
-        <v>0</v>
-      </c>
-      <c r="J8" s="113">
-        <v>0</v>
-      </c>
-      <c r="K8" s="113">
-        <v>1</v>
-      </c>
-      <c r="L8" s="113">
-        <v>1</v>
-      </c>
-      <c r="M8" s="113">
-        <v>0</v>
-      </c>
-      <c r="N8" s="113">
-        <v>0</v>
-      </c>
-      <c r="O8" s="113">
-        <v>0</v>
-      </c>
-      <c r="P8" s="113">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="113">
-        <v>0</v>
-      </c>
-      <c r="R8" s="113">
-        <v>0</v>
-      </c>
-      <c r="S8" s="113">
-        <v>1</v>
-      </c>
-      <c r="T8" s="113">
-        <v>0</v>
-      </c>
-      <c r="U8" s="113">
-        <v>0</v>
-      </c>
-      <c r="V8" s="113">
-        <v>0</v>
-      </c>
-      <c r="W8" s="113">
-        <f>SUM(B8:V8)</f>
-        <v>3</v>
-      </c>
-      <c r="Z8"/>
-    </row>
-    <row r="9" spans="1:26" customHeight="1" ht="18">
-      <c r="A9" s="114" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="115">
-        <v>0</v>
-      </c>
-      <c r="C9" s="115">
-        <v>0</v>
-      </c>
-      <c r="D9" s="115">
-        <v>0</v>
-      </c>
-      <c r="E9" s="115">
-        <v>0</v>
-      </c>
-      <c r="F9" s="115">
-        <v>0</v>
-      </c>
-      <c r="G9" s="115">
-        <v>0</v>
-      </c>
-      <c r="H9" s="115">
-        <v>0</v>
-      </c>
-      <c r="I9" s="115">
-        <v>0</v>
-      </c>
-      <c r="J9" s="115">
-        <v>0</v>
-      </c>
-      <c r="K9" s="115">
-        <v>0</v>
-      </c>
-      <c r="L9" s="115">
-        <v>0</v>
-      </c>
-      <c r="M9" s="115">
-        <v>0</v>
-      </c>
-      <c r="N9" s="115">
-        <v>0</v>
-      </c>
-      <c r="O9" s="115">
-        <v>0</v>
-      </c>
-      <c r="P9" s="115">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="115">
-        <v>1</v>
-      </c>
-      <c r="R9" s="115">
-        <v>0</v>
-      </c>
-      <c r="S9" s="115">
-        <v>1</v>
-      </c>
-      <c r="T9" s="115">
-        <v>0</v>
-      </c>
-      <c r="U9" s="115">
-        <v>0</v>
-      </c>
-      <c r="V9" s="115">
-        <v>0</v>
-      </c>
-      <c r="W9" s="113">
-        <f>SUM(B9:V9)</f>
-        <v>2</v>
-      </c>
-      <c r="Z9"/>
-    </row>
-    <row r="10" spans="1:26" customHeight="1" ht="18">
-      <c r="A10" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="113">
-        <v>0</v>
-      </c>
-      <c r="C10" s="113">
-        <v>0</v>
-      </c>
-      <c r="D10" s="113">
-        <v>0</v>
-      </c>
-      <c r="E10" s="113">
-        <v>0</v>
-      </c>
-      <c r="F10" s="113">
-        <v>0</v>
-      </c>
-      <c r="G10" s="113">
-        <v>0</v>
-      </c>
-      <c r="H10" s="113">
-        <v>0</v>
-      </c>
-      <c r="I10" s="113">
-        <v>0</v>
-      </c>
-      <c r="J10" s="113">
-        <v>0</v>
-      </c>
-      <c r="K10" s="113">
-        <v>0</v>
-      </c>
-      <c r="L10" s="113">
-        <v>0</v>
-      </c>
-      <c r="M10" s="113">
-        <v>0</v>
-      </c>
-      <c r="N10" s="113">
-        <v>0</v>
-      </c>
-      <c r="O10" s="113">
-        <v>0</v>
-      </c>
-      <c r="P10" s="113">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="113">
-        <v>0</v>
-      </c>
-      <c r="R10" s="113">
-        <v>0</v>
-      </c>
-      <c r="S10" s="113">
-        <v>0</v>
-      </c>
-      <c r="T10" s="113">
-        <v>1</v>
-      </c>
-      <c r="U10" s="113">
-        <v>1</v>
-      </c>
-      <c r="V10" s="113">
-        <v>0</v>
-      </c>
-      <c r="W10" s="113">
-        <f>SUM(B10:V10)</f>
-        <v>2</v>
-      </c>
-      <c r="Z10"/>
-    </row>
-    <row r="11" spans="1:26" customHeight="1" ht="18">
-      <c r="A11" s="114" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="115">
-        <v>0</v>
-      </c>
-      <c r="C11" s="115">
-        <v>0</v>
-      </c>
-      <c r="D11" s="115">
-        <v>0</v>
-      </c>
-      <c r="E11" s="115">
-        <v>0</v>
-      </c>
-      <c r="F11" s="115">
-        <v>0</v>
-      </c>
-      <c r="G11" s="115">
-        <v>0</v>
-      </c>
-      <c r="H11" s="115">
-        <v>0</v>
-      </c>
-      <c r="I11" s="115">
-        <v>0</v>
-      </c>
-      <c r="J11" s="115">
-        <v>0</v>
-      </c>
-      <c r="K11" s="115">
-        <v>0</v>
-      </c>
-      <c r="L11" s="115">
-        <v>0</v>
-      </c>
-      <c r="M11" s="115">
-        <v>1</v>
-      </c>
-      <c r="N11" s="115">
-        <v>0</v>
-      </c>
-      <c r="O11" s="115">
-        <v>0</v>
-      </c>
-      <c r="P11" s="115">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="115">
-        <v>0</v>
-      </c>
-      <c r="R11" s="115">
-        <v>0</v>
-      </c>
-      <c r="S11" s="115">
-        <v>0</v>
-      </c>
-      <c r="T11" s="115">
-        <v>0</v>
-      </c>
-      <c r="U11" s="115">
-        <v>0</v>
-      </c>
-      <c r="V11" s="115">
-        <v>0</v>
-      </c>
-      <c r="W11" s="113">
-        <f>SUM(B11:V11)</f>
-        <v>1</v>
-      </c>
-      <c r="Z11"/>
+    <row r="7" spans="1:26" customHeight="1" ht="15.75">
+      <c r="A7" s="116"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
+      <c r="K7" s="116"/>
+      <c r="L7" s="116"/>
+      <c r="M7" s="116"/>
+      <c r="N7" s="116"/>
+      <c r="O7" s="116"/>
+      <c r="P7" s="116"/>
+      <c r="Q7" s="116"/>
+      <c r="R7" s="116"/>
+      <c r="S7" s="116"/>
+      <c r="T7" s="116"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="116"/>
+      <c r="W7" s="116"/>
+    </row>
+    <row r="8" spans="1:26" customHeight="1" ht="15.75">
+      <c r="A8" s="116"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="116"/>
+      <c r="U8" s="116"/>
+      <c r="V8" s="116"/>
+      <c r="W8" s="116"/>
+    </row>
+    <row r="9" spans="1:26" customHeight="1" ht="15.75">
+      <c r="A9" s="116"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="116"/>
+      <c r="Q9" s="116"/>
+      <c r="R9" s="116"/>
+      <c r="S9" s="116"/>
+      <c r="T9" s="116"/>
+      <c r="U9" s="116"/>
+      <c r="V9" s="116"/>
+      <c r="W9" s="116"/>
+    </row>
+    <row r="10" spans="1:26" customHeight="1" ht="15.75">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="116"/>
+    </row>
+    <row r="11" spans="1:26" customHeight="1" ht="15.75">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
+      <c r="T11" s="116"/>
+      <c r="U11" s="116"/>
+      <c r="V11" s="116"/>
+      <c r="W11" s="116"/>
     </row>
     <row r="12" spans="1:26" customHeight="1" ht="15.75">
       <c r="A12" s="116"/>
@@ -49004,131 +48782,6 @@
       <c r="V1001" s="116"/>
       <c r="W1001" s="116"/>
     </row>
-    <row r="1002" spans="1:26" customHeight="1" ht="15.75">
-      <c r="A1002" s="116"/>
-      <c r="B1002" s="116"/>
-      <c r="C1002" s="116"/>
-      <c r="D1002" s="116"/>
-      <c r="E1002" s="116"/>
-      <c r="F1002" s="116"/>
-      <c r="G1002" s="116"/>
-      <c r="H1002" s="116"/>
-      <c r="I1002" s="116"/>
-      <c r="J1002" s="116"/>
-      <c r="K1002" s="116"/>
-      <c r="L1002" s="116"/>
-      <c r="M1002" s="116"/>
-      <c r="N1002" s="116"/>
-      <c r="O1002" s="116"/>
-      <c r="P1002" s="116"/>
-      <c r="Q1002" s="116"/>
-      <c r="R1002" s="116"/>
-      <c r="S1002" s="116"/>
-      <c r="T1002" s="116"/>
-      <c r="U1002" s="116"/>
-      <c r="V1002" s="116"/>
-      <c r="W1002" s="116"/>
-    </row>
-    <row r="1003" spans="1:26" customHeight="1" ht="15.75">
-      <c r="A1003" s="116"/>
-      <c r="B1003" s="116"/>
-      <c r="C1003" s="116"/>
-      <c r="D1003" s="116"/>
-      <c r="E1003" s="116"/>
-      <c r="F1003" s="116"/>
-      <c r="G1003" s="116"/>
-      <c r="H1003" s="116"/>
-      <c r="I1003" s="116"/>
-      <c r="J1003" s="116"/>
-      <c r="K1003" s="116"/>
-      <c r="L1003" s="116"/>
-      <c r="M1003" s="116"/>
-      <c r="N1003" s="116"/>
-      <c r="O1003" s="116"/>
-      <c r="P1003" s="116"/>
-      <c r="Q1003" s="116"/>
-      <c r="R1003" s="116"/>
-      <c r="S1003" s="116"/>
-      <c r="T1003" s="116"/>
-      <c r="U1003" s="116"/>
-      <c r="V1003" s="116"/>
-      <c r="W1003" s="116"/>
-    </row>
-    <row r="1004" spans="1:26" customHeight="1" ht="15.75">
-      <c r="A1004" s="116"/>
-      <c r="B1004" s="116"/>
-      <c r="C1004" s="116"/>
-      <c r="D1004" s="116"/>
-      <c r="E1004" s="116"/>
-      <c r="F1004" s="116"/>
-      <c r="G1004" s="116"/>
-      <c r="H1004" s="116"/>
-      <c r="I1004" s="116"/>
-      <c r="J1004" s="116"/>
-      <c r="K1004" s="116"/>
-      <c r="L1004" s="116"/>
-      <c r="M1004" s="116"/>
-      <c r="N1004" s="116"/>
-      <c r="O1004" s="116"/>
-      <c r="P1004" s="116"/>
-      <c r="Q1004" s="116"/>
-      <c r="R1004" s="116"/>
-      <c r="S1004" s="116"/>
-      <c r="T1004" s="116"/>
-      <c r="U1004" s="116"/>
-      <c r="V1004" s="116"/>
-      <c r="W1004" s="116"/>
-    </row>
-    <row r="1005" spans="1:26" customHeight="1" ht="15.75">
-      <c r="A1005" s="116"/>
-      <c r="B1005" s="116"/>
-      <c r="C1005" s="116"/>
-      <c r="D1005" s="116"/>
-      <c r="E1005" s="116"/>
-      <c r="F1005" s="116"/>
-      <c r="G1005" s="116"/>
-      <c r="H1005" s="116"/>
-      <c r="I1005" s="116"/>
-      <c r="J1005" s="116"/>
-      <c r="K1005" s="116"/>
-      <c r="L1005" s="116"/>
-      <c r="M1005" s="116"/>
-      <c r="N1005" s="116"/>
-      <c r="O1005" s="116"/>
-      <c r="P1005" s="116"/>
-      <c r="Q1005" s="116"/>
-      <c r="R1005" s="116"/>
-      <c r="S1005" s="116"/>
-      <c r="T1005" s="116"/>
-      <c r="U1005" s="116"/>
-      <c r="V1005" s="116"/>
-      <c r="W1005" s="116"/>
-    </row>
-    <row r="1006" spans="1:26" customHeight="1" ht="15.75">
-      <c r="A1006" s="116"/>
-      <c r="B1006" s="116"/>
-      <c r="C1006" s="116"/>
-      <c r="D1006" s="116"/>
-      <c r="E1006" s="116"/>
-      <c r="F1006" s="116"/>
-      <c r="G1006" s="116"/>
-      <c r="H1006" s="116"/>
-      <c r="I1006" s="116"/>
-      <c r="J1006" s="116"/>
-      <c r="K1006" s="116"/>
-      <c r="L1006" s="116"/>
-      <c r="M1006" s="116"/>
-      <c r="N1006" s="116"/>
-      <c r="O1006" s="116"/>
-      <c r="P1006" s="116"/>
-      <c r="Q1006" s="116"/>
-      <c r="R1006" s="116"/>
-      <c r="S1006" s="116"/>
-      <c r="T1006" s="116"/>
-      <c r="U1006" s="116"/>
-      <c r="V1006" s="116"/>
-      <c r="W1006" s="116"/>
-    </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <mergeCells>
